--- a/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
+++ b/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>WR/DB</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -675,7 +675,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>WR/DB</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -714,7 +714,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>WR/DB</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -831,7 +831,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>TE/DB</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -870,7 +870,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>TE/OL/DL</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -987,7 +987,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>WR/DB</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -1065,7 +1065,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -1182,11 +1182,11 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Adean Abdelqader</t>
+          <t>Aedan Abdelqader</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATH/K</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -1255,45 +1255,6 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Sal Ahmed</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DL/LB</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1656,7 +1617,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>

--- a/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
+++ b/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1255,6 +1255,45 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Sal Ahmad</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DL/LB</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
+++ b/game-stats/Week1_WarBred_vs_Falestine-Falcons.xlsx
@@ -3755,13 +3755,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="29" min="1" max="1"/>
     <col width="22" customWidth="1" style="29" min="2" max="2"/>
     <col width="14" customWidth="1" style="29" min="3" max="3"/>
     <col width="12" customWidth="1" style="29" min="4" max="17"/>
+    <col width="10" customWidth="1" style="29" min="11" max="11"/>
     <col width="10" customWidth="1" style="29" min="15" max="15"/>
     <col width="8.710000000000001" customWidth="1" style="29" min="18" max="32"/>
   </cols>
@@ -3817,42 +3818,47 @@
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="K1" s="25" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>Rush TD</t>
+        </is>
+      </c>
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="L1" s="25" t="inlineStr">
+      <c r="M1" s="25" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="M1" s="25" t="inlineStr">
+      <c r="N1" s="25" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="N1" s="25" t="inlineStr">
+      <c r="O1" s="25" t="inlineStr">
         <is>
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="O1" s="30" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>Def TDs</t>
         </is>
       </c>
-      <c r="P1" s="25" t="inlineStr">
+      <c r="Q1" s="25" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="25" t="inlineStr">
+      <c r="R1" s="25" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="25" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -3883,7 +3889,7 @@
       <c r="J2" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="28" t="n">
+      <c r="K2" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="28" t="n">
@@ -3895,14 +3901,17 @@
       <c r="N2" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="28" t="n"/>
-      <c r="Q2" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="28" t="n"/>
       <c r="R2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3939,7 +3948,7 @@
       <c r="J3" s="28" t="n">
         <v>42</v>
       </c>
-      <c r="K3" s="28" t="n">
+      <c r="K3" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="28" t="n">
@@ -3951,14 +3960,17 @@
       <c r="N3" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="28" t="n"/>
-      <c r="Q3" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="28" t="n"/>
       <c r="R3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="28" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3987,7 +3999,7 @@
       <c r="J4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="28" t="n">
@@ -3999,14 +4011,17 @@
       <c r="N4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="28" t="n"/>
-      <c r="Q4" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="28" t="n"/>
       <c r="R4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="28" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4035,7 +4050,7 @@
       <c r="J5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="28" t="n">
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="28" t="n">
@@ -4047,14 +4062,17 @@
       <c r="N5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="28" t="n"/>
-      <c r="Q5" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="28" t="n"/>
       <c r="R5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4085,7 +4103,7 @@
       <c r="J6" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="K6" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="28" t="n">
@@ -4097,14 +4115,17 @@
       <c r="N6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="28" t="n"/>
-      <c r="Q6" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="28" t="n"/>
       <c r="R6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4133,26 +4154,29 @@
       <c r="J7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="28" t="n">
+      <c r="K7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="28" t="n">
+      <c r="M7" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="M7" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="28" t="n"/>
-      <c r="Q7" s="28" t="n">
+      <c r="O7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="28" t="n"/>
+      <c r="R7" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="28" t="n">
+      <c r="S7" s="28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4181,7 +4205,7 @@
       <c r="J8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="28" t="n">
@@ -4193,14 +4217,17 @@
       <c r="N8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="28" t="n"/>
       <c r="R8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4229,7 +4256,7 @@
       <c r="J9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="28" t="n">
+      <c r="K9" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="28" t="n">
@@ -4241,14 +4268,17 @@
       <c r="N9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="28" t="n"/>
       <c r="R9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4277,26 +4307,29 @@
       <c r="J10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="28" t="n">
+      <c r="M10" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="M10" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="28" t="n"/>
       <c r="R10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4325,7 +4358,7 @@
       <c r="J11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="28" t="n">
+      <c r="K11" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="28" t="n">
@@ -4337,14 +4370,17 @@
       <c r="N11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="28" t="n"/>
       <c r="R11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4373,7 +4409,7 @@
       <c r="J12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="28" t="n">
@@ -4385,14 +4421,17 @@
       <c r="N12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="28" t="n"/>
       <c r="R12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4421,28 +4460,31 @@
       <c r="J13" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="28" t="n">
+      <c r="K13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="28" t="n">
+      <c r="M13" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="M13" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="28" t="n">
+      <c r="O13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4479,7 +4521,7 @@
       <c r="J14" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="31" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="28" t="n">
@@ -4491,14 +4533,17 @@
       <c r="N14" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="28" t="n"/>
       <c r="R14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="28" t="n">
         <v>0</v>
       </c>
     </row>
